--- a/results/CB/ResponseCBsCorrected.xlsx
+++ b/results/CB/ResponseCBsCorrected.xlsx
@@ -33486,7 +33486,7 @@
         <v>3474</v>
       </c>
       <c r="B1740" t="n">
-        <v>6344</v>
+        <v>3172</v>
       </c>
       <c r="C1740" t="n">
         <v>11.13</v>
@@ -33503,7 +33503,7 @@
         <v>3475</v>
       </c>
       <c r="B1741" t="n">
-        <v>6345</v>
+        <v>3173</v>
       </c>
       <c r="C1741" t="n">
         <v>12.67</v>
@@ -33520,7 +33520,7 @@
         <v>3476</v>
       </c>
       <c r="B1742" t="n">
-        <v>6346</v>
+        <v>3174</v>
       </c>
       <c r="C1742" t="n">
         <v>11.73</v>
@@ -33537,7 +33537,7 @@
         <v>3477</v>
       </c>
       <c r="B1743" t="n">
-        <v>6347</v>
+        <v>3175</v>
       </c>
       <c r="C1743" t="n">
         <v>14</v>
@@ -33554,7 +33554,7 @@
         <v>3478</v>
       </c>
       <c r="B1744" t="n">
-        <v>6348</v>
+        <v>3176</v>
       </c>
       <c r="C1744" t="n">
         <v>12.4</v>
@@ -33571,7 +33571,7 @@
         <v>3479</v>
       </c>
       <c r="B1745" t="n">
-        <v>6349</v>
+        <v>3177</v>
       </c>
       <c r="C1745" t="n">
         <v>12.94</v>
@@ -33588,7 +33588,7 @@
         <v>3480</v>
       </c>
       <c r="B1746" t="n">
-        <v>6350</v>
+        <v>3178</v>
       </c>
       <c r="C1746" t="n">
         <v>12.37</v>
@@ -33605,7 +33605,7 @@
         <v>3481</v>
       </c>
       <c r="B1747" t="n">
-        <v>6351</v>
+        <v>3179</v>
       </c>
       <c r="C1747" t="n">
         <v>26.7</v>
@@ -33622,7 +33622,7 @@
         <v>3482</v>
       </c>
       <c r="B1748" t="n">
-        <v>6352</v>
+        <v>3180</v>
       </c>
       <c r="C1748" t="n">
         <v>16.89</v>
@@ -33639,7 +33639,7 @@
         <v>3483</v>
       </c>
       <c r="B1749" t="n">
-        <v>6353</v>
+        <v>3181</v>
       </c>
       <c r="C1749" t="n">
         <v>11.99</v>
@@ -33656,7 +33656,7 @@
         <v>3484</v>
       </c>
       <c r="B1750" t="n">
-        <v>6354</v>
+        <v>3182</v>
       </c>
       <c r="C1750" t="n">
         <v>30</v>
@@ -33673,7 +33673,7 @@
         <v>3485</v>
       </c>
       <c r="B1751" t="n">
-        <v>6355</v>
+        <v>3183</v>
       </c>
       <c r="C1751" t="n">
         <v>30</v>
@@ -33690,7 +33690,7 @@
         <v>3486</v>
       </c>
       <c r="B1752" t="n">
-        <v>6356</v>
+        <v>3184</v>
       </c>
       <c r="C1752" t="n">
         <v>30</v>
@@ -33707,7 +33707,7 @@
         <v>3487</v>
       </c>
       <c r="B1753" t="n">
-        <v>6357</v>
+        <v>3185</v>
       </c>
       <c r="C1753" t="n">
         <v>30</v>
@@ -33724,7 +33724,7 @@
         <v>3488</v>
       </c>
       <c r="B1754" t="n">
-        <v>6358</v>
+        <v>3186</v>
       </c>
       <c r="C1754" t="n">
         <v>30</v>
@@ -33741,7 +33741,7 @@
         <v>3489</v>
       </c>
       <c r="B1755" t="n">
-        <v>6359</v>
+        <v>3187</v>
       </c>
       <c r="C1755" t="n">
         <v>30</v>
@@ -33758,7 +33758,7 @@
         <v>3490</v>
       </c>
       <c r="B1756" t="n">
-        <v>6360</v>
+        <v>3188</v>
       </c>
       <c r="C1756" t="n">
         <v>30</v>
@@ -33775,7 +33775,7 @@
         <v>3491</v>
       </c>
       <c r="B1757" t="n">
-        <v>6361</v>
+        <v>3189</v>
       </c>
       <c r="C1757" t="n">
         <v>30</v>
@@ -33792,7 +33792,7 @@
         <v>3492</v>
       </c>
       <c r="B1758" t="n">
-        <v>6362</v>
+        <v>3190</v>
       </c>
       <c r="C1758" t="n">
         <v>30</v>
@@ -33809,7 +33809,7 @@
         <v>3493</v>
       </c>
       <c r="B1759" t="n">
-        <v>6363</v>
+        <v>3191</v>
       </c>
       <c r="C1759" t="n">
         <v>30</v>
